--- a/data/trans_camb/IP7_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP7_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 5,29</t>
+          <t>-0,49; 5,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 3,04</t>
+          <t>-1,44; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 6,92</t>
+          <t>-1,17; 7,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,47</t>
+          <t>-1,86; 4,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 5,33</t>
+          <t>-1,61; 5,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 12,58</t>
+          <t>-0,1; 12,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,82</t>
+          <t>-0,31; 3,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,21</t>
+          <t>-0,78; 3,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 7,86</t>
+          <t>0,49; 7,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-73,82; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 610,39</t>
+          <t>-61,01; 659,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 679,23</t>
+          <t>-55,82; 791,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 1434,2</t>
+          <t>-37,3; 1515,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 582,84</t>
+          <t>-19,44; 539,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 414,17</t>
+          <t>-40,65; 420,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 959,8</t>
+          <t>-8,54; 942,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,26</t>
+          <t>-0,19; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,96</t>
+          <t>-0,07; 4,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,79</t>
+          <t>-0,67; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,13; -0,92</t>
+          <t>-4,94; -0,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; -0,56</t>
+          <t>-4,8; -0,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 0,84</t>
+          <t>-3,95; 1,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,45</t>
+          <t>-2,1; 0,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,83</t>
+          <t>-1,99; 0,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,45</t>
+          <t>-1,92; 1,42</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,12; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 1491,94</t>
+          <t>-40,58; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-94,73; -28,66</t>
+          <t>-100,0; -29,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-93,21; 8,44</t>
+          <t>-92,89; -4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,51; 70,39</t>
+          <t>-85,44; 66,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 39,04</t>
+          <t>-72,14; 47,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,74; 71,82</t>
+          <t>-69,01; 75,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 102,08</t>
+          <t>-68,06; 105,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,61</t>
+          <t>-2,81; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,66</t>
+          <t>-3,53; 1,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,55</t>
+          <t>-1,77; 4,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,96</t>
+          <t>-6,66; 1,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,2</t>
+          <t>-7,27; 0,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,24</t>
+          <t>-7,07; 0,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,84</t>
+          <t>-3,66; 1,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 0,04</t>
+          <t>-4,41; 0,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 1,42</t>
+          <t>-3,42; 1,52</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,74; 344,37</t>
+          <t>-81,06; 389,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-90,37; 272,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 661,85</t>
+          <t>-60,62; 574,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 40,55</t>
+          <t>-81,69; 46,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,17; 34,09</t>
+          <t>-85,56; 26,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 43,16</t>
+          <t>-87,68; 19,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 40,27</t>
+          <t>-69,05; 46,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,12; 7,0</t>
+          <t>-78,94; 15,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,13; 63,74</t>
+          <t>-64,72; 64,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 1,72</t>
+          <t>-3,35; 1,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,54</t>
+          <t>-3,34; 1,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 8,11</t>
+          <t>-2,06; 7,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,0</t>
+          <t>-1,93; 3,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,07</t>
+          <t>-3,48; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,84</t>
+          <t>-3,75; 1,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,03</t>
+          <t>-2,21; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,01</t>
+          <t>-2,85; 0,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,23</t>
+          <t>-2,11; 3,27</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-84,58; 128,41</t>
+          <t>-80,49; 98,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,27; 105,96</t>
+          <t>-78,93; 160,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,8; 536,93</t>
+          <t>-64,57; 488,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 201,98</t>
+          <t>-49,34; 232,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 141,06</t>
+          <t>-82,05; 141,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,34; 70,95</t>
+          <t>-81,04; 91,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,49; 106,33</t>
+          <t>-55,73; 99,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 58,04</t>
+          <t>-71,58; 50,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 155,38</t>
+          <t>-59,62; 151,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,83</t>
+          <t>-0,54; 1,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,34</t>
+          <t>-1,0; 1,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,36</t>
+          <t>-0,11; 4,65</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,41</t>
+          <t>-2,48; 0,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -0,04</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,46</t>
+          <t>-2,52; 0,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,68</t>
+          <t>-1,18; 0,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,25</t>
+          <t>-1,58; 0,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,68</t>
+          <t>-0,93; 1,84</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 162,32</t>
+          <t>-27,26; 157,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 117,53</t>
+          <t>-44,5; 113,0</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 350,64</t>
+          <t>-11,13; 340,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 14,7</t>
+          <t>-57,91; 15,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 3,64</t>
+          <t>-66,7; -0,63</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,17; 20,14</t>
+          <t>-58,11; 20,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,2; 31,75</t>
+          <t>-36,41; 35,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-48,15; 13,67</t>
+          <t>-48,32; 9,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 74,12</t>
+          <t>-31,55; 76,54</t>
         </is>
       </c>
     </row>
